--- a/OSPAR_meta_analysis.xlsx
+++ b/OSPAR_meta_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/loftyj_cardiff_ac_uk/Documents/Postdoc/OSPAR datasets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44e2464d2a9165ff/Postdoc/OSPAR datasets/github download/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{74E7EE81-44CF-8F4B-A1E8-0CC2A7B18031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD642014-15A0-B144-B1E7-7B2A5416B8E9}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{74E7EE81-44CF-8F4B-A1E8-0CC2A7B18031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B2D392-D8C2-4FA4-9CB6-C2C272D0BBB7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -428,21 +431,12 @@
     <t>Indistinguishable plastic pieces 2.5–50 cm (hard plastic)</t>
   </si>
   <si>
-    <t>Hard plastic pieces  2.5–50 cm</t>
-  </si>
-  <si>
     <t>Plastic films or fragments 2.5–50 cm (soft plastic)</t>
   </si>
   <si>
-    <t>Soft plastic pieces/films 2.5–50 cm</t>
-  </si>
-  <si>
     <t>Indistinguishable pieces of polystyrene 0–2.5 cm (estimated)</t>
   </si>
   <si>
-    <t>Foam plastic pieces  2.5 - 50 cm</t>
-  </si>
-  <si>
     <t>Plastic pieces &gt; 50 cm (hard plastic)</t>
   </si>
   <si>
@@ -716,18 +710,9 @@
     <t>Indistinguishable plastic pieces 0–2.5 cm (hard plastic)</t>
   </si>
   <si>
-    <t>Hard plastic pieces 0.5–2.5 cm</t>
-  </si>
-  <si>
     <t>Plastic films or fragments 0–2.5 cm (soft plastic)</t>
   </si>
   <si>
-    <t>Soft plastic pieces/films 0.5–2.5 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foam plastic pieces 0.5–2.5 cm </t>
-  </si>
-  <si>
     <t>Disposable BBQs</t>
   </si>
   <si>
@@ -741,6 +726,24 @@
   </si>
   <si>
     <t>flexibility</t>
+  </si>
+  <si>
+    <t>Soft plastic pieces/films 2.5-50 cm</t>
+  </si>
+  <si>
+    <t>Hard plastic pieces 0.5-2.5 cm</t>
+  </si>
+  <si>
+    <t>Soft plastic pieces/films 0.5-2.5 cm</t>
+  </si>
+  <si>
+    <t>Foam plastic pieces 0.5-2.5 cm</t>
+  </si>
+  <si>
+    <t>Hard plastic pieces 2.5-50 cm</t>
+  </si>
+  <si>
+    <t>Foam plastic pieces 2.5-50 cm</t>
   </si>
 </sst>
 </file>
@@ -1110,72 +1113,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="104.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="104.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="33.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="42.83203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="39.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="39.83203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="48.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="33" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="31.42578125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="36" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="37.83203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="34.83203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="47" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="51.5" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="48.1640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="52.1640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="35" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="31.1640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="34.83203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="34.83203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="31.1640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="35" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,10 +1201,10 @@
         <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
@@ -1357,7 +1360,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -1539,7 +1542,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1568,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K3">
         <v>394</v>
@@ -1721,7 +1724,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K4">
         <v>240</v>
@@ -1903,7 +1906,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1932,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K5">
         <v>941</v>
@@ -2085,7 +2088,7 @@
         <v>0.1540041067761807</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K6">
         <v>643</v>
@@ -2267,7 +2270,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K7">
         <v>1547</v>
@@ -2449,7 +2452,7 @@
         <v>0.25667351129363453</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K8">
         <v>870</v>
@@ -2631,7 +2634,7 @@
         <v>0.30800821355236141</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2660,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K9">
         <v>215</v>
@@ -2813,7 +2816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K10">
         <v>2934</v>
@@ -2995,7 +2998,7 @@
         <v>0.87268993839835718</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3024,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K11">
         <v>508</v>
@@ -3177,7 +3180,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K12">
         <v>141</v>
@@ -3359,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K13">
         <v>30</v>
@@ -3541,7 +3544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3570,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K14">
         <v>4</v>
@@ -3723,7 +3726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K15">
         <v>46</v>
@@ -3905,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K16">
         <v>63</v>
@@ -4087,7 +4090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4116,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K17">
         <v>25</v>
@@ -4269,7 +4272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4298,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K18">
         <v>33</v>
@@ -4451,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4480,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K19">
         <v>5447</v>
@@ -4633,7 +4636,7 @@
         <v>1.7967145790554411</v>
       </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4662,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K20">
         <v>452</v>
@@ -4815,7 +4818,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4844,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K21">
         <v>217</v>
@@ -4997,7 +5000,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5026,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K22">
         <v>21</v>
@@ -5179,7 +5182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5208,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K23">
         <v>8500</v>
@@ -5361,7 +5364,7 @@
         <v>1.4887063655030801</v>
       </c>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -5390,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K24">
         <v>399</v>
@@ -5543,7 +5546,7 @@
         <v>0.30800821355236141</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -5572,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K25">
         <v>745</v>
@@ -5725,7 +5728,7 @@
         <v>0.20533880903490759</v>
       </c>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -5754,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K26">
         <v>1240</v>
@@ -5907,7 +5910,7 @@
         <v>0.25667351129363453</v>
       </c>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5936,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K27">
         <v>54</v>
@@ -6089,7 +6092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -6118,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K28">
         <v>570</v>
@@ -6271,7 +6274,7 @@
         <v>0.35934291581108829</v>
       </c>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -6300,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K29">
         <v>398</v>
@@ -6453,7 +6456,7 @@
         <v>0.35934291581108829</v>
       </c>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -6482,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K30">
         <v>65</v>
@@ -6635,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -6664,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K31">
         <v>9</v>
@@ -6817,7 +6820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -6846,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -6999,7 +7002,7 @@
         <v>0.1540041067761807</v>
       </c>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -7028,7 +7031,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K33">
         <v>34</v>
@@ -7181,7 +7184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -7210,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K34">
         <v>806</v>
@@ -7363,7 +7366,7 @@
         <v>0.1540041067761807</v>
       </c>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -7392,7 +7395,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K35">
         <v>315</v>
@@ -7545,7 +7548,7 @@
         <v>0.46201232032854211</v>
       </c>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -7574,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K36">
         <v>51</v>
@@ -7727,7 +7730,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -7756,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K37">
         <v>272</v>
@@ -7909,7 +7912,7 @@
         <v>0.30800821355236141</v>
       </c>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -7938,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K38">
         <v>27</v>
@@ -8091,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -8120,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K39">
         <v>196</v>
@@ -8273,7 +8276,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -8302,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K40">
         <v>208</v>
@@ -8455,7 +8458,7 @@
         <v>0.1540041067761807</v>
       </c>
     </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -8484,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K41">
         <v>371</v>
@@ -8637,7 +8640,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -8666,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K42">
         <v>76</v>
@@ -8819,7 +8822,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -8848,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K43">
         <v>451</v>
@@ -9001,7 +9004,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -9030,7 +9033,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -9183,7 +9186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -9212,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K45">
         <v>90</v>
@@ -9365,7 +9368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -9394,7 +9397,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K46">
         <v>34</v>
@@ -9547,7 +9550,7 @@
         <v>0.56468172484599588</v>
       </c>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -9564,7 +9567,7 @@
         <v>130</v>
       </c>
       <c r="F47" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="G47">
         <v>830</v>
@@ -9576,7 +9579,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K47">
         <v>6029</v>
@@ -9729,7 +9732,7 @@
         <v>3.64476386036961</v>
       </c>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -9743,10 +9746,10 @@
         <v>59</v>
       </c>
       <c r="E48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F48" t="s">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="G48">
         <v>890</v>
@@ -9758,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K48">
         <v>20263</v>
@@ -9911,7 +9914,7 @@
         <v>1.0266940451745381</v>
       </c>
     </row>
-    <row r="49" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -9925,10 +9928,10 @@
         <v>78</v>
       </c>
       <c r="E49" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F49" t="s">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="G49">
         <v>10</v>
@@ -9940,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K49">
         <v>9791</v>
@@ -10093,7 +10096,7 @@
         <v>3.4394250513347031</v>
       </c>
     </row>
-    <row r="50" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -10107,10 +10110,10 @@
         <v>72</v>
       </c>
       <c r="E50" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F50" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G50">
         <v>830</v>
@@ -10122,7 +10125,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K50">
         <v>520</v>
@@ -10275,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -10289,10 +10292,10 @@
         <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G51">
         <v>890</v>
@@ -10304,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K51">
         <v>456</v>
@@ -10457,7 +10460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -10471,10 +10474,10 @@
         <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F52" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G52">
         <v>10</v>
@@ -10486,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K52">
         <v>68</v>
@@ -10639,7 +10642,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -10650,13 +10653,13 @@
         <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E53" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G53">
         <v>890</v>
@@ -10668,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K53">
         <v>2518</v>
@@ -10821,7 +10824,7 @@
         <v>0.46201232032854211</v>
       </c>
     </row>
-    <row r="54" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -10835,10 +10838,10 @@
         <v>72</v>
       </c>
       <c r="E54" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F54" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G54">
         <v>830</v>
@@ -10850,7 +10853,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K54">
         <v>3</v>
@@ -11003,7 +11006,7 @@
         <v>0.30800821355236141</v>
       </c>
     </row>
-    <row r="55" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -11011,16 +11014,16 @@
         <v>49</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G55">
         <v>1100</v>
@@ -11032,7 +11035,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K55">
         <v>138</v>
@@ -11185,7 +11188,7 @@
         <v>0.20533880903490759</v>
       </c>
     </row>
-    <row r="56" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -11193,16 +11196,16 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
+        <v>142</v>
+      </c>
+      <c r="D56" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" t="s">
         <v>145</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
         <v>145</v>
-      </c>
-      <c r="E56" t="s">
-        <v>148</v>
-      </c>
-      <c r="F56" t="s">
-        <v>148</v>
       </c>
       <c r="G56">
         <v>1100</v>
@@ -11214,7 +11217,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K56">
         <v>10</v>
@@ -11367,7 +11370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -11375,16 +11378,16 @@
         <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E57" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F57" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G57">
         <v>1100</v>
@@ -11396,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K57">
         <v>216</v>
@@ -11549,7 +11552,7 @@
         <v>0.51334702258726894</v>
       </c>
     </row>
-    <row r="58" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -11557,16 +11560,16 @@
         <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F58" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G58">
         <v>1300</v>
@@ -11578,7 +11581,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K58">
         <v>110</v>
@@ -11731,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -11739,16 +11742,16 @@
         <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D59" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E59" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F59" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G59">
         <v>1300</v>
@@ -11760,7 +11763,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K59">
         <v>15</v>
@@ -11913,7 +11916,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -11921,16 +11924,16 @@
         <v>57</v>
       </c>
       <c r="C60" t="s">
+        <v>148</v>
+      </c>
+      <c r="D60" t="s">
+        <v>148</v>
+      </c>
+      <c r="E60" t="s">
         <v>151</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
         <v>151</v>
-      </c>
-      <c r="E60" t="s">
-        <v>154</v>
-      </c>
-      <c r="F60" t="s">
-        <v>154</v>
       </c>
       <c r="G60">
         <v>1300</v>
@@ -11942,7 +11945,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K60">
         <v>59</v>
@@ -12095,7 +12098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -12103,16 +12106,16 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E61" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F61" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G61">
         <v>1300</v>
@@ -12124,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K61">
         <v>1627</v>
@@ -12277,7 +12280,7 @@
         <v>0.30800821355236141</v>
       </c>
     </row>
-    <row r="62" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -12285,16 +12288,16 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D62" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G62">
         <v>600</v>
@@ -12306,7 +12309,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K62">
         <v>156</v>
@@ -12459,7 +12462,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -12467,16 +12470,16 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
+        <v>154</v>
+      </c>
+      <c r="D63" t="s">
+        <v>154</v>
+      </c>
+      <c r="E63" t="s">
+        <v>156</v>
+      </c>
+      <c r="F63" t="s">
         <v>157</v>
-      </c>
-      <c r="D63" t="s">
-        <v>157</v>
-      </c>
-      <c r="E63" t="s">
-        <v>159</v>
-      </c>
-      <c r="F63" t="s">
-        <v>160</v>
       </c>
       <c r="G63">
         <v>600</v>
@@ -12488,7 +12491,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K63">
         <v>180</v>
@@ -12641,7 +12644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -12649,16 +12652,16 @@
         <v>62.1</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E64" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F64" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G64">
         <v>600</v>
@@ -12670,7 +12673,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K64">
         <v>207</v>
@@ -12823,7 +12826,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="65" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -12837,10 +12840,10 @@
         <v>95</v>
       </c>
       <c r="E65" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G65">
         <v>890</v>
@@ -12852,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K65">
         <v>196</v>
@@ -13005,7 +13008,7 @@
         <v>0.35934291581108829</v>
       </c>
     </row>
-    <row r="66" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -13019,10 +13022,10 @@
         <v>95</v>
       </c>
       <c r="E66" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F66" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G66">
         <v>890</v>
@@ -13034,7 +13037,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K66">
         <v>598</v>
@@ -13187,7 +13190,7 @@
         <v>3.4907597535934292</v>
       </c>
     </row>
-    <row r="67" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -13195,16 +13198,16 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E67" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F67" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G67">
         <v>600</v>
@@ -13216,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K67">
         <v>28</v>
@@ -13369,7 +13372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -13377,16 +13380,16 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D68" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E68" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F68" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G68">
         <v>600</v>
@@ -13398,7 +13401,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K68">
         <v>27</v>
@@ -13551,7 +13554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -13559,16 +13562,16 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D69" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E69" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F69" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G69">
         <v>600</v>
@@ -13580,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K69">
         <v>364</v>
@@ -13733,7 +13736,7 @@
         <v>0.25667351129363453</v>
       </c>
     </row>
-    <row r="70" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -13741,16 +13744,16 @@
         <v>67.099999999999994</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D70" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E70" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F70" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G70">
         <v>600</v>
@@ -13762,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K70">
         <v>172</v>
@@ -13915,7 +13918,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -13923,16 +13926,16 @@
         <v>68</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D71" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F71" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G71">
         <v>300</v>
@@ -13944,7 +13947,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K71">
         <v>111</v>
@@ -14097,7 +14100,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -14105,16 +14108,16 @@
         <v>69</v>
       </c>
       <c r="C72" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F72" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G72">
         <v>300</v>
@@ -14126,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -14279,7 +14282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -14287,16 +14290,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" t="s">
         <v>172</v>
       </c>
-      <c r="D73" t="s">
+      <c r="F73" t="s">
         <v>172</v>
-      </c>
-      <c r="E73" t="s">
-        <v>175</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73">
         <v>300</v>
@@ -14308,7 +14311,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K73">
         <v>10</v>
@@ -14461,7 +14464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -14469,16 +14472,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E74" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F74" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G74">
         <v>300</v>
@@ -14490,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K74">
         <v>15</v>
@@ -14643,7 +14646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -14651,16 +14654,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E75" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G75">
         <v>300</v>
@@ -14672,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K75">
         <v>613</v>
@@ -14825,7 +14828,7 @@
         <v>0.56468172484599588</v>
       </c>
     </row>
-    <row r="76" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -14833,16 +14836,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E76" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F76" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G76">
         <v>300</v>
@@ -14854,7 +14857,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K76">
         <v>327</v>
@@ -15007,7 +15010,7 @@
         <v>0.20533880903490759</v>
       </c>
     </row>
-    <row r="77" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -15015,16 +15018,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D77" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E77" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F77" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G77">
         <v>2700</v>
@@ -15036,7 +15039,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K77">
         <v>85</v>
@@ -15189,7 +15192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -15197,16 +15200,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="s">
+        <v>178</v>
+      </c>
+      <c r="D78" t="s">
+        <v>178</v>
+      </c>
+      <c r="E78" t="s">
+        <v>180</v>
+      </c>
+      <c r="F78" t="s">
         <v>181</v>
-      </c>
-      <c r="D78" t="s">
-        <v>181</v>
-      </c>
-      <c r="E78" t="s">
-        <v>183</v>
-      </c>
-      <c r="F78" t="s">
-        <v>184</v>
       </c>
       <c r="G78">
         <v>2700</v>
@@ -15218,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K78">
         <v>235</v>
@@ -15371,7 +15374,7 @@
         <v>42.145790554414788</v>
       </c>
     </row>
-    <row r="79" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -15379,16 +15382,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D79" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E79" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F79" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G79">
         <v>30</v>
@@ -15400,7 +15403,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K79">
         <v>882</v>
@@ -15553,7 +15556,7 @@
         <v>2.669404517453799</v>
       </c>
     </row>
-    <row r="80" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -15561,16 +15564,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E80" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F80" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G80">
         <v>2700</v>
@@ -15582,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K80">
         <v>48</v>
@@ -15735,7 +15738,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="81" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -15743,16 +15746,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D81" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E81" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F81" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G81">
         <v>2700</v>
@@ -15764,7 +15767,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K81">
         <v>21</v>
@@ -15917,7 +15920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -15925,16 +15928,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E82" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F82" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G82">
         <v>2700</v>
@@ -15946,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K82">
         <v>608</v>
@@ -16099,7 +16102,7 @@
         <v>0.61601642710472282</v>
       </c>
     </row>
-    <row r="83" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -16107,16 +16110,16 @@
         <v>81.099999999999994</v>
       </c>
       <c r="C83" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D83" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E83" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F83" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G83">
         <v>2700</v>
@@ -16128,7 +16131,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K83">
         <v>57</v>
@@ -16281,7 +16284,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -16289,16 +16292,16 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E84" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F84" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G84">
         <v>2700</v>
@@ -16310,7 +16313,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K84">
         <v>65</v>
@@ -16463,7 +16466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -16471,16 +16474,16 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D85" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E85" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F85" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G85">
         <v>2700</v>
@@ -16492,7 +16495,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K85">
         <v>79</v>
@@ -16645,7 +16648,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -16653,16 +16656,16 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D86" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E86" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G86">
         <v>2700</v>
@@ -16674,7 +16677,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K86">
         <v>1</v>
@@ -16827,7 +16830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -16835,16 +16838,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D87" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E87" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F87" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G87">
         <v>2700</v>
@@ -16856,7 +16859,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K87">
         <v>3</v>
@@ -17009,7 +17012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -17017,16 +17020,16 @@
         <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D88" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E88" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F88" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G88">
         <v>2700</v>
@@ -17038,7 +17041,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K88">
         <v>39</v>
@@ -17191,7 +17194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -17199,16 +17202,16 @@
         <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D89" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E89" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F89" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G89">
         <v>2700</v>
@@ -17220,7 +17223,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K89">
         <v>160</v>
@@ -17373,7 +17376,7 @@
         <v>0.71868583162217659</v>
       </c>
     </row>
-    <row r="90" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -17381,16 +17384,16 @@
         <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E90" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F90" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G90">
         <v>2700</v>
@@ -17402,7 +17405,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K90">
         <v>42</v>
@@ -17555,7 +17558,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -17563,16 +17566,16 @@
         <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D91" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E91" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F91" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G91">
         <v>600</v>
@@ -17584,7 +17587,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K91">
         <v>588</v>
@@ -17737,7 +17740,7 @@
         <v>0.87268993839835718</v>
       </c>
     </row>
-    <row r="92" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -17745,16 +17748,16 @@
         <v>92</v>
       </c>
       <c r="C92" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92" t="s">
+        <v>197</v>
+      </c>
+      <c r="E92" t="s">
         <v>200</v>
       </c>
-      <c r="D92" t="s">
+      <c r="F92" t="s">
         <v>200</v>
-      </c>
-      <c r="E92" t="s">
-        <v>203</v>
-      </c>
-      <c r="F92" t="s">
-        <v>203</v>
       </c>
       <c r="G92">
         <v>2200</v>
@@ -17766,7 +17769,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K92">
         <v>43</v>
@@ -17919,7 +17922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -17927,16 +17930,16 @@
         <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E93" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G93">
         <v>2200</v>
@@ -17948,7 +17951,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K93">
         <v>218</v>
@@ -18101,7 +18104,7 @@
         <v>20.790554414784388</v>
       </c>
     </row>
-    <row r="94" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -18112,13 +18115,13 @@
         <v>81</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E94" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F94" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G94">
         <v>1100</v>
@@ -18130,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K94">
         <v>35</v>
@@ -18283,7 +18286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -18297,10 +18300,10 @@
         <v>75</v>
       </c>
       <c r="E95" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F95" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G95">
         <v>1040</v>
@@ -18312,7 +18315,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K95">
         <v>2109</v>
@@ -18465,7 +18468,7 @@
         <v>1.129363449691992</v>
       </c>
     </row>
-    <row r="96" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -18476,13 +18479,13 @@
         <v>81</v>
       </c>
       <c r="D96" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E96" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F96" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G96">
         <v>600</v>
@@ -18494,7 +18497,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K96">
         <v>7</v>
@@ -18647,7 +18650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -18661,10 +18664,10 @@
         <v>95</v>
       </c>
       <c r="E97" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F97" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G97">
         <v>890</v>
@@ -18676,7 +18679,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K97">
         <v>912</v>
@@ -18829,7 +18832,7 @@
         <v>0.30800821355236141</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -18843,10 +18846,10 @@
         <v>95</v>
       </c>
       <c r="E98" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F98" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G98">
         <v>890</v>
@@ -18858,7 +18861,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K98">
         <v>140</v>
@@ -19011,7 +19014,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -19022,13 +19025,13 @@
         <v>81</v>
       </c>
       <c r="D99" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E99" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F99" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G99">
         <v>600</v>
@@ -19040,7 +19043,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K99">
         <v>66</v>
@@ -19193,7 +19196,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -19204,13 +19207,13 @@
         <v>81</v>
       </c>
       <c r="D100" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E100" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F100" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G100">
         <v>890</v>
@@ -19222,7 +19225,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K100">
         <v>276</v>
@@ -19375,7 +19378,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -19389,10 +19392,10 @@
         <v>59</v>
       </c>
       <c r="E101" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F101" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G101">
         <v>890</v>
@@ -19404,7 +19407,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K101">
         <v>620</v>
@@ -19557,7 +19560,7 @@
         <v>0.25667351129363453</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -19568,13 +19571,13 @@
         <v>81</v>
       </c>
       <c r="D102" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E102" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F102" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G102">
         <v>600</v>
@@ -19586,7 +19589,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K102">
         <v>63</v>
@@ -19739,7 +19742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -19753,10 +19756,10 @@
         <v>95</v>
       </c>
       <c r="E103" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G103">
         <v>890</v>
@@ -19768,7 +19771,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K103">
         <v>121</v>
@@ -19921,7 +19924,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -19935,10 +19938,10 @@
         <v>72</v>
       </c>
       <c r="E104" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F104" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G104">
         <v>830</v>
@@ -19950,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K104">
         <v>47</v>
@@ -20103,7 +20106,7 @@
         <v>5.1334702258726897E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -20114,13 +20117,13 @@
         <v>81</v>
       </c>
       <c r="D105" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E105" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F105" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G105">
         <v>890</v>
@@ -20132,7 +20135,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K105">
         <v>162</v>
@@ -20285,7 +20288,7 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -20299,10 +20302,10 @@
         <v>59</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F106" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G106">
         <v>890</v>
@@ -20314,7 +20317,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K106">
         <v>19</v>
@@ -20467,7 +20470,7 @@
         <v>0.56468172484599588</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -20481,10 +20484,10 @@
         <v>72</v>
       </c>
       <c r="E107" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F107" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G107">
         <v>830</v>
@@ -20496,7 +20499,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K107">
         <v>7808</v>
@@ -20649,7 +20652,7 @@
         <v>2.258726899383984</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -20663,10 +20666,10 @@
         <v>59</v>
       </c>
       <c r="E108" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F108" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G108">
         <v>890</v>
@@ -20678,7 +20681,7 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K108">
         <v>14231</v>
@@ -20831,7 +20834,7 @@
         <v>0.92402464065708423</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -20845,10 +20848,10 @@
         <v>78</v>
       </c>
       <c r="E109" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F109" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G109">
         <v>10</v>
@@ -20860,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K109">
         <v>9205</v>
@@ -21013,7 +21016,7 @@
         <v>1.899383983572895</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -21021,16 +21024,16 @@
         <v>120</v>
       </c>
       <c r="C110" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D110" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E110" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G110">
         <v>2700</v>
@@ -21042,7 +21045,7 @@
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K110">
         <v>21</v>
@@ -21195,13 +21198,13 @@
         <v>0.10266940451745379</v>
       </c>
     </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F113" s="2"/>
     </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F114" s="2"/>
     </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F115" s="2"/>
     </row>
   </sheetData>
